--- a/irrbb_calc/output/irrbb_report.xlsx
+++ b/irrbb_calc/output/irrbb_report.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E2" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I2" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -533,28 +533,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E3" t="n">
-        <v>564941749.88</v>
+        <v>584447213.12</v>
       </c>
       <c r="F3" t="n">
-        <v>-3401887.860000014</v>
+        <v>-29938964.05999994</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2126179912500009</v>
+        <v>-2.494913671666662</v>
       </c>
       <c r="H3" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I3" t="n">
-        <v>2458096736.1</v>
+        <v>2181936002.53</v>
       </c>
       <c r="J3" t="n">
-        <v>33778705.04999971</v>
+        <v>7679372.740000248</v>
       </c>
       <c r="K3" t="n">
-        <v>2.111169065624982</v>
+        <v>0.639947728333354</v>
       </c>
     </row>
     <row r="4">
@@ -572,28 +572,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E4" t="n">
-        <v>559119349.5700001</v>
+        <v>597394594.91</v>
       </c>
       <c r="F4" t="n">
-        <v>-9224288.169999957</v>
+        <v>-16991582.26999998</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5765180106249973</v>
+        <v>-1.415965189166665</v>
       </c>
       <c r="H4" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I4" t="n">
-        <v>2481860090.69</v>
+        <v>2210930152.52</v>
       </c>
       <c r="J4" t="n">
-        <v>57542059.63999987</v>
+        <v>36673522.73000002</v>
       </c>
       <c r="K4" t="n">
-        <v>3.596378727499991</v>
+        <v>3.056126894166668</v>
       </c>
     </row>
     <row r="5">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E5" t="n">
-        <v>543419870.96</v>
+        <v>571846923.42</v>
       </c>
       <c r="F5" t="n">
-        <v>-24923766.77999997</v>
+        <v>-42539253.75999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.557735423749998</v>
+        <v>-3.544937813333333</v>
       </c>
       <c r="H5" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I5" t="n">
-        <v>2570934764.39</v>
+        <v>2267212933.25</v>
       </c>
       <c r="J5" t="n">
-        <v>146616733.3399997</v>
+        <v>92956303.46000004</v>
       </c>
       <c r="K5" t="n">
-        <v>9.16354583374998</v>
+        <v>7.74635862166667</v>
       </c>
     </row>
     <row r="6">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E6" t="n">
-        <v>595604777.72</v>
+        <v>657013128.1</v>
       </c>
       <c r="F6" t="n">
-        <v>27261139.98000002</v>
+        <v>42626950.92000008</v>
       </c>
       <c r="G6" t="n">
-        <v>1.703821248750001</v>
+        <v>3.552245910000006</v>
       </c>
       <c r="H6" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I6" t="n">
-        <v>2289576861.54</v>
+        <v>2088879685.01</v>
       </c>
       <c r="J6" t="n">
-        <v>-134741169.5100002</v>
+        <v>-85376944.77999997</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.421323094375015</v>
+        <v>-7.11474539833333</v>
       </c>
     </row>
     <row r="7">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E7" t="n">
-        <v>563205377.86</v>
+        <v>623974966.02</v>
       </c>
       <c r="F7" t="n">
-        <v>-5138259.879999995</v>
+        <v>9588788.840000033</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3211412424999997</v>
+        <v>0.7990657366666696</v>
       </c>
       <c r="H7" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I7" t="n">
-        <v>2452319419.53</v>
+        <v>2204808001.51</v>
       </c>
       <c r="J7" t="n">
-        <v>28001388.48000002</v>
+        <v>30551371.72000027</v>
       </c>
       <c r="K7" t="n">
-        <v>1.750086780000001</v>
+        <v>2.545947643333355</v>
       </c>
     </row>
     <row r="8">
@@ -728,28 +728,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E8" t="n">
-        <v>575902873.34</v>
+        <v>604742509.74</v>
       </c>
       <c r="F8" t="n">
-        <v>7559235.600000024</v>
+        <v>-9643667.439999938</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4724522250000014</v>
+        <v>-0.8036389533333281</v>
       </c>
       <c r="H8" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I8" t="n">
-        <v>2397400495.19</v>
+        <v>2145100116.98</v>
       </c>
       <c r="J8" t="n">
-        <v>-26917535.86000013</v>
+        <v>-29156512.80999994</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.682345991250008</v>
+        <v>-2.429709400833329</v>
       </c>
     </row>
     <row r="9">
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E9" t="n">
-        <v>577077882.63</v>
+        <v>647366157.4400001</v>
       </c>
       <c r="F9" t="n">
-        <v>8734244.889999986</v>
+        <v>32979980.26000011</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5458903056249991</v>
+        <v>2.748331688333343</v>
       </c>
       <c r="H9" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="I9" t="n">
-        <v>2378544175.29</v>
+        <v>2158367069.35</v>
       </c>
       <c r="J9" t="n">
-        <v>-45773855.76000023</v>
+        <v>-15889560.44000006</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.860865985000014</v>
+        <v>-1.324130036666671</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D2" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D3" t="n">
-        <v>564941749.88</v>
+        <v>584447213.12</v>
       </c>
       <c r="E3" t="n">
-        <v>-3401887.860000014</v>
+        <v>-29938964.05999994</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2126179912500009</v>
+        <v>-2.494913671666662</v>
       </c>
     </row>
     <row r="4">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D4" t="n">
-        <v>559119349.5700001</v>
+        <v>597394594.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-9224288.169999957</v>
+        <v>-16991582.26999998</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5765180106249973</v>
+        <v>-1.415965189166665</v>
       </c>
     </row>
     <row r="5">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D5" t="n">
-        <v>543419870.96</v>
+        <v>571846923.42</v>
       </c>
       <c r="E5" t="n">
-        <v>-24923766.77999997</v>
+        <v>-42539253.75999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.557735423749998</v>
+        <v>-3.544937813333333</v>
       </c>
     </row>
     <row r="6">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D6" t="n">
-        <v>595604777.72</v>
+        <v>657013128.1</v>
       </c>
       <c r="E6" t="n">
-        <v>27261139.98000002</v>
+        <v>42626950.92000008</v>
       </c>
       <c r="F6" t="n">
-        <v>1.703821248750001</v>
+        <v>3.552245910000006</v>
       </c>
     </row>
     <row r="7">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D7" t="n">
-        <v>563205377.86</v>
+        <v>623974966.02</v>
       </c>
       <c r="E7" t="n">
-        <v>-5138259.879999995</v>
+        <v>9588788.840000033</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3211412424999997</v>
+        <v>0.7990657366666696</v>
       </c>
     </row>
     <row r="8">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D8" t="n">
-        <v>575902873.34</v>
+        <v>604742509.74</v>
       </c>
       <c r="E8" t="n">
-        <v>7559235.600000024</v>
+        <v>-9643667.439999938</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4724522250000014</v>
+        <v>-0.8036389533333281</v>
       </c>
     </row>
     <row r="9">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>568343637.74</v>
+        <v>614386177.1799999</v>
       </c>
       <c r="D9" t="n">
-        <v>577077882.63</v>
+        <v>647366157.4400001</v>
       </c>
       <c r="E9" t="n">
-        <v>8734244.889999986</v>
+        <v>32979980.26000011</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5458903056249991</v>
+        <v>2.748331688333343</v>
       </c>
     </row>
   </sheetData>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D2" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D3" t="n">
-        <v>2458096736.1</v>
+        <v>2181936002.53</v>
       </c>
       <c r="E3" t="n">
-        <v>33778705.04999971</v>
+        <v>7679372.740000248</v>
       </c>
       <c r="F3" t="n">
-        <v>2.111169065624982</v>
+        <v>0.639947728333354</v>
       </c>
     </row>
     <row r="4">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D4" t="n">
-        <v>2481860090.69</v>
+        <v>2210930152.52</v>
       </c>
       <c r="E4" t="n">
-        <v>57542059.63999987</v>
+        <v>36673522.73000002</v>
       </c>
       <c r="F4" t="n">
-        <v>3.596378727499991</v>
+        <v>3.056126894166668</v>
       </c>
     </row>
     <row r="5">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D5" t="n">
-        <v>2570934764.39</v>
+        <v>2267212933.25</v>
       </c>
       <c r="E5" t="n">
-        <v>146616733.3399997</v>
+        <v>92956303.46000004</v>
       </c>
       <c r="F5" t="n">
-        <v>9.16354583374998</v>
+        <v>7.74635862166667</v>
       </c>
     </row>
     <row r="6">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D6" t="n">
-        <v>2289576861.54</v>
+        <v>2088879685.01</v>
       </c>
       <c r="E6" t="n">
-        <v>-134741169.5100002</v>
+        <v>-85376944.77999997</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.421323094375015</v>
+        <v>-7.11474539833333</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D7" t="n">
-        <v>2452319419.53</v>
+        <v>2204808001.51</v>
       </c>
       <c r="E7" t="n">
-        <v>28001388.48000002</v>
+        <v>30551371.72000027</v>
       </c>
       <c r="F7" t="n">
-        <v>1.750086780000001</v>
+        <v>2.545947643333355</v>
       </c>
     </row>
     <row r="8">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D8" t="n">
-        <v>2397400495.19</v>
+        <v>2145100116.98</v>
       </c>
       <c r="E8" t="n">
-        <v>-26917535.86000013</v>
+        <v>-29156512.80999994</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.682345991250008</v>
+        <v>-2.429709400833329</v>
       </c>
     </row>
     <row r="9">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2424318031.05</v>
+        <v>2174256629.79</v>
       </c>
       <c r="D9" t="n">
-        <v>2378544175.29</v>
+        <v>2158367069.35</v>
       </c>
       <c r="E9" t="n">
-        <v>-45773855.76000023</v>
+        <v>-15889560.44000006</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.860865985000014</v>
+        <v>-1.324130036666671</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/irrbb_report.xlsx
+++ b/irrbb_calc/output/irrbb_report.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E2" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I2" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -533,28 +533,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E3" t="n">
-        <v>584447213.12</v>
+        <v>595587989.5599999</v>
       </c>
       <c r="F3" t="n">
-        <v>-29938964.05999994</v>
+        <v>-16482595.10000002</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.494913671666662</v>
+        <v>-1.373549591666669</v>
       </c>
       <c r="H3" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I3" t="n">
-        <v>2181936002.53</v>
+        <v>2190935799.46</v>
       </c>
       <c r="J3" t="n">
-        <v>7679372.740000248</v>
+        <v>-1311343.389999866</v>
       </c>
       <c r="K3" t="n">
-        <v>0.639947728333354</v>
+        <v>-0.1092786158333222</v>
       </c>
     </row>
     <row r="4">
@@ -572,28 +572,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E4" t="n">
-        <v>597394594.91</v>
+        <v>590585952.03</v>
       </c>
       <c r="F4" t="n">
-        <v>-16991582.26999998</v>
+        <v>-21484632.63</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.415965189166665</v>
+        <v>-1.790386052499999</v>
       </c>
       <c r="H4" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I4" t="n">
-        <v>2210930152.52</v>
+        <v>2216973654.4</v>
       </c>
       <c r="J4" t="n">
-        <v>36673522.73000002</v>
+        <v>24726511.55000019</v>
       </c>
       <c r="K4" t="n">
-        <v>3.056126894166668</v>
+        <v>2.060542629166683</v>
       </c>
     </row>
     <row r="5">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E5" t="n">
-        <v>571846923.42</v>
+        <v>555254424.24</v>
       </c>
       <c r="F5" t="n">
-        <v>-42539253.75999999</v>
+        <v>-56816160.41999996</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.544937813333333</v>
+        <v>-4.734680034999996</v>
       </c>
       <c r="H5" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I5" t="n">
-        <v>2267212933.25</v>
+        <v>2253653018.34</v>
       </c>
       <c r="J5" t="n">
-        <v>92956303.46000004</v>
+        <v>61405875.49000025</v>
       </c>
       <c r="K5" t="n">
-        <v>7.74635862166667</v>
+        <v>5.117156290833353</v>
       </c>
     </row>
     <row r="6">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E6" t="n">
-        <v>657013128.1</v>
+        <v>673143847.5700001</v>
       </c>
       <c r="F6" t="n">
-        <v>42626950.92000008</v>
+        <v>61073262.91000009</v>
       </c>
       <c r="G6" t="n">
-        <v>3.552245910000006</v>
+        <v>5.08943857583334</v>
       </c>
       <c r="H6" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I6" t="n">
-        <v>2088879685.01</v>
+        <v>2135795552.07</v>
       </c>
       <c r="J6" t="n">
-        <v>-85376944.77999997</v>
+        <v>-56451590.77999997</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.11474539833333</v>
+        <v>-4.704299231666664</v>
       </c>
     </row>
     <row r="7">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E7" t="n">
-        <v>623974966.02</v>
+        <v>606993370.22</v>
       </c>
       <c r="F7" t="n">
-        <v>9588788.840000033</v>
+        <v>-5077214.439999938</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7990657366666696</v>
+        <v>-0.4231012033333282</v>
       </c>
       <c r="H7" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I7" t="n">
-        <v>2204808001.51</v>
+        <v>2219037258.94</v>
       </c>
       <c r="J7" t="n">
-        <v>30551371.72000027</v>
+        <v>26790116.09000015</v>
       </c>
       <c r="K7" t="n">
-        <v>2.545947643333355</v>
+        <v>2.232509674166679</v>
       </c>
     </row>
     <row r="8">
@@ -728,28 +728,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E8" t="n">
-        <v>604742509.74</v>
+        <v>621226231.51</v>
       </c>
       <c r="F8" t="n">
-        <v>-9643667.439999938</v>
+        <v>9155646.850000024</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8036389533333281</v>
+        <v>0.7629705708333353</v>
       </c>
       <c r="H8" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I8" t="n">
-        <v>2145100116.98</v>
+        <v>2167308510.39</v>
       </c>
       <c r="J8" t="n">
-        <v>-29156512.80999994</v>
+        <v>-24938632.46000004</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.429709400833329</v>
+        <v>-2.07821937166667</v>
       </c>
     </row>
     <row r="9">
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E9" t="n">
-        <v>647366157.4400001</v>
+        <v>638606894.7</v>
       </c>
       <c r="F9" t="n">
-        <v>32979980.26000011</v>
+        <v>26536310.04000008</v>
       </c>
       <c r="G9" t="n">
-        <v>2.748331688333343</v>
+        <v>2.211359170000007</v>
       </c>
       <c r="H9" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="I9" t="n">
-        <v>2158367069.35</v>
+        <v>2188335533.43</v>
       </c>
       <c r="J9" t="n">
-        <v>-15889560.44000006</v>
+        <v>-3911609.420000076</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.324130036666671</v>
+        <v>-0.325967451666673</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D2" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D3" t="n">
-        <v>584447213.12</v>
+        <v>595587989.5599999</v>
       </c>
       <c r="E3" t="n">
-        <v>-29938964.05999994</v>
+        <v>-16482595.10000002</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.494913671666662</v>
+        <v>-1.373549591666669</v>
       </c>
     </row>
     <row r="4">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D4" t="n">
-        <v>597394594.91</v>
+        <v>590585952.03</v>
       </c>
       <c r="E4" t="n">
-        <v>-16991582.26999998</v>
+        <v>-21484632.63</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.415965189166665</v>
+        <v>-1.790386052499999</v>
       </c>
     </row>
     <row r="5">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D5" t="n">
-        <v>571846923.42</v>
+        <v>555254424.24</v>
       </c>
       <c r="E5" t="n">
-        <v>-42539253.75999999</v>
+        <v>-56816160.41999996</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.544937813333333</v>
+        <v>-4.734680034999996</v>
       </c>
     </row>
     <row r="6">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D6" t="n">
-        <v>657013128.1</v>
+        <v>673143847.5700001</v>
       </c>
       <c r="E6" t="n">
-        <v>42626950.92000008</v>
+        <v>61073262.91000009</v>
       </c>
       <c r="F6" t="n">
-        <v>3.552245910000006</v>
+        <v>5.08943857583334</v>
       </c>
     </row>
     <row r="7">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D7" t="n">
-        <v>623974966.02</v>
+        <v>606993370.22</v>
       </c>
       <c r="E7" t="n">
-        <v>9588788.840000033</v>
+        <v>-5077214.439999938</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7990657366666696</v>
+        <v>-0.4231012033333282</v>
       </c>
     </row>
     <row r="8">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D8" t="n">
-        <v>604742509.74</v>
+        <v>621226231.51</v>
       </c>
       <c r="E8" t="n">
-        <v>-9643667.439999938</v>
+        <v>9155646.850000024</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8036389533333281</v>
+        <v>0.7629705708333353</v>
       </c>
     </row>
     <row r="9">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>614386177.1799999</v>
+        <v>612070584.66</v>
       </c>
       <c r="D9" t="n">
-        <v>647366157.4400001</v>
+        <v>638606894.7</v>
       </c>
       <c r="E9" t="n">
-        <v>32979980.26000011</v>
+        <v>26536310.04000008</v>
       </c>
       <c r="F9" t="n">
-        <v>2.748331688333343</v>
+        <v>2.211359170000007</v>
       </c>
     </row>
   </sheetData>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D2" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D3" t="n">
-        <v>2181936002.53</v>
+        <v>2190935799.46</v>
       </c>
       <c r="E3" t="n">
-        <v>7679372.740000248</v>
+        <v>-1311343.389999866</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639947728333354</v>
+        <v>-0.1092786158333222</v>
       </c>
     </row>
     <row r="4">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D4" t="n">
-        <v>2210930152.52</v>
+        <v>2216973654.4</v>
       </c>
       <c r="E4" t="n">
-        <v>36673522.73000002</v>
+        <v>24726511.55000019</v>
       </c>
       <c r="F4" t="n">
-        <v>3.056126894166668</v>
+        <v>2.060542629166683</v>
       </c>
     </row>
     <row r="5">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D5" t="n">
-        <v>2267212933.25</v>
+        <v>2253653018.34</v>
       </c>
       <c r="E5" t="n">
-        <v>92956303.46000004</v>
+        <v>61405875.49000025</v>
       </c>
       <c r="F5" t="n">
-        <v>7.74635862166667</v>
+        <v>5.117156290833353</v>
       </c>
     </row>
     <row r="6">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D6" t="n">
-        <v>2088879685.01</v>
+        <v>2135795552.07</v>
       </c>
       <c r="E6" t="n">
-        <v>-85376944.77999997</v>
+        <v>-56451590.77999997</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.11474539833333</v>
+        <v>-4.704299231666664</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D7" t="n">
-        <v>2204808001.51</v>
+        <v>2219037258.94</v>
       </c>
       <c r="E7" t="n">
-        <v>30551371.72000027</v>
+        <v>26790116.09000015</v>
       </c>
       <c r="F7" t="n">
-        <v>2.545947643333355</v>
+        <v>2.232509674166679</v>
       </c>
     </row>
     <row r="8">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D8" t="n">
-        <v>2145100116.98</v>
+        <v>2167308510.39</v>
       </c>
       <c r="E8" t="n">
-        <v>-29156512.80999994</v>
+        <v>-24938632.46000004</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.429709400833329</v>
+        <v>-2.07821937166667</v>
       </c>
     </row>
     <row r="9">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2174256629.79</v>
+        <v>2192247142.85</v>
       </c>
       <c r="D9" t="n">
-        <v>2158367069.35</v>
+        <v>2188335533.43</v>
       </c>
       <c r="E9" t="n">
-        <v>-15889560.44000006</v>
+        <v>-3911609.420000076</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.324130036666671</v>
+        <v>-0.325967451666673</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/irrbb_report.xlsx
+++ b/irrbb_calc/output/irrbb_report.xlsx
@@ -481,7 +481,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E2" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I2" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -533,33 +533,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E3" t="n">
-        <v>595587989.5599999</v>
+        <v>508247205.35</v>
       </c>
       <c r="F3" t="n">
-        <v>-16482595.10000002</v>
+        <v>-22015439.62</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.373549591666669</v>
+        <v>-1.834619968333334</v>
       </c>
       <c r="H3" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I3" t="n">
-        <v>2190935799.46</v>
+        <v>2038240148.16</v>
       </c>
       <c r="J3" t="n">
-        <v>-1311343.389999866</v>
+        <v>29776835.74000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1092786158333222</v>
+        <v>2.481402978333334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E4" t="n">
-        <v>590585952.03</v>
+        <v>510874107.55</v>
       </c>
       <c r="F4" t="n">
-        <v>-21484632.63</v>
+        <v>-19388537.42000002</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.790386052499999</v>
+        <v>-1.615711451666668</v>
       </c>
       <c r="H4" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I4" t="n">
-        <v>2216973654.4</v>
+        <v>2055152460</v>
       </c>
       <c r="J4" t="n">
-        <v>24726511.55000019</v>
+        <v>46689147.57999992</v>
       </c>
       <c r="K4" t="n">
-        <v>2.060542629166683</v>
+        <v>3.890762298333327</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -611,33 +611,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E5" t="n">
-        <v>555254424.24</v>
+        <v>484366736.45</v>
       </c>
       <c r="F5" t="n">
-        <v>-56816160.41999996</v>
+        <v>-45895908.52000004</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.734680034999996</v>
+        <v>-3.824659043333337</v>
       </c>
       <c r="H5" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I5" t="n">
-        <v>2253653018.34</v>
+        <v>2128346249.82</v>
       </c>
       <c r="J5" t="n">
-        <v>61405875.49000025</v>
+        <v>119882937.3999999</v>
       </c>
       <c r="K5" t="n">
-        <v>5.117156290833353</v>
+        <v>9.990244783333321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,33 +650,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E6" t="n">
-        <v>673143847.5700001</v>
+        <v>572674499.95</v>
       </c>
       <c r="F6" t="n">
-        <v>61073262.91000009</v>
+        <v>42411854.98000002</v>
       </c>
       <c r="G6" t="n">
-        <v>5.08943857583334</v>
+        <v>3.534321248333335</v>
       </c>
       <c r="H6" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I6" t="n">
-        <v>2135795552.07</v>
+        <v>1899204219.51</v>
       </c>
       <c r="J6" t="n">
-        <v>-56451590.77999997</v>
+        <v>-109259092.9100001</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.704299231666664</v>
+        <v>-9.104924409166674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -689,33 +689,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E7" t="n">
-        <v>606993370.22</v>
+        <v>528746533.87</v>
       </c>
       <c r="F7" t="n">
-        <v>-5077214.439999938</v>
+        <v>-1516111.100000024</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4231012033333282</v>
+        <v>-0.1263425916666686</v>
       </c>
       <c r="H7" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I7" t="n">
-        <v>2219037258.94</v>
+        <v>2028925382.35</v>
       </c>
       <c r="J7" t="n">
-        <v>26790116.09000015</v>
+        <v>20462069.92999983</v>
       </c>
       <c r="K7" t="n">
-        <v>2.232509674166679</v>
+        <v>1.705172494166652</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -728,33 +728,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E8" t="n">
-        <v>621226231.51</v>
+        <v>528129393.9</v>
       </c>
       <c r="F8" t="n">
-        <v>9155646.850000024</v>
+        <v>-2133251.070000052</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7629705708333353</v>
+        <v>-0.1777709225000044</v>
       </c>
       <c r="H8" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I8" t="n">
-        <v>2167308510.39</v>
+        <v>1988438779.55</v>
       </c>
       <c r="J8" t="n">
-        <v>-24938632.46000004</v>
+        <v>-20024532.87000012</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.07821937166667</v>
+        <v>-1.66871107250001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E9" t="n">
-        <v>638606894.7</v>
+        <v>552727420.49</v>
       </c>
       <c r="F9" t="n">
-        <v>26536310.04000008</v>
+        <v>22464775.51999998</v>
       </c>
       <c r="G9" t="n">
-        <v>2.211359170000007</v>
+        <v>1.872064626666665</v>
       </c>
       <c r="H9" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="I9" t="n">
-        <v>2188335533.43</v>
+        <v>1969035458.72</v>
       </c>
       <c r="J9" t="n">
-        <v>-3911609.420000076</v>
+        <v>-39427853.70000005</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.325967451666673</v>
+        <v>-3.285654475000004</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D2" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D3" t="n">
-        <v>595587989.5599999</v>
+        <v>508247205.35</v>
       </c>
       <c r="E3" t="n">
-        <v>-16482595.10000002</v>
+        <v>-22015439.62</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.373549591666669</v>
+        <v>-1.834619968333334</v>
       </c>
     </row>
     <row r="4">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D4" t="n">
-        <v>590585952.03</v>
+        <v>510874107.55</v>
       </c>
       <c r="E4" t="n">
-        <v>-21484632.63</v>
+        <v>-19388537.42000002</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.790386052499999</v>
+        <v>-1.615711451666668</v>
       </c>
     </row>
     <row r="5">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D5" t="n">
-        <v>555254424.24</v>
+        <v>484366736.45</v>
       </c>
       <c r="E5" t="n">
-        <v>-56816160.41999996</v>
+        <v>-45895908.52000004</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.734680034999996</v>
+        <v>-3.824659043333337</v>
       </c>
     </row>
     <row r="6">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D6" t="n">
-        <v>673143847.5700001</v>
+        <v>572674499.95</v>
       </c>
       <c r="E6" t="n">
-        <v>61073262.91000009</v>
+        <v>42411854.98000002</v>
       </c>
       <c r="F6" t="n">
-        <v>5.08943857583334</v>
+        <v>3.534321248333335</v>
       </c>
     </row>
     <row r="7">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D7" t="n">
-        <v>606993370.22</v>
+        <v>528746533.87</v>
       </c>
       <c r="E7" t="n">
-        <v>-5077214.439999938</v>
+        <v>-1516111.100000024</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4231012033333282</v>
+        <v>-0.1263425916666686</v>
       </c>
     </row>
     <row r="8">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D8" t="n">
-        <v>621226231.51</v>
+        <v>528129393.9</v>
       </c>
       <c r="E8" t="n">
-        <v>9155646.850000024</v>
+        <v>-2133251.070000052</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7629705708333353</v>
+        <v>-0.1777709225000044</v>
       </c>
     </row>
     <row r="9">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>612070584.66</v>
+        <v>530262644.97</v>
       </c>
       <c r="D9" t="n">
-        <v>638606894.7</v>
+        <v>552727420.49</v>
       </c>
       <c r="E9" t="n">
-        <v>26536310.04000008</v>
+        <v>22464775.51999998</v>
       </c>
       <c r="F9" t="n">
-        <v>2.211359170000007</v>
+        <v>1.872064626666665</v>
       </c>
     </row>
   </sheetData>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D2" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D3" t="n">
-        <v>2190935799.46</v>
+        <v>2038240148.16</v>
       </c>
       <c r="E3" t="n">
-        <v>-1311343.389999866</v>
+        <v>29776835.74000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1092786158333222</v>
+        <v>2.481402978333334</v>
       </c>
     </row>
     <row r="4">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D4" t="n">
-        <v>2216973654.4</v>
+        <v>2055152460</v>
       </c>
       <c r="E4" t="n">
-        <v>24726511.55000019</v>
+        <v>46689147.57999992</v>
       </c>
       <c r="F4" t="n">
-        <v>2.060542629166683</v>
+        <v>3.890762298333327</v>
       </c>
     </row>
     <row r="5">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D5" t="n">
-        <v>2253653018.34</v>
+        <v>2128346249.82</v>
       </c>
       <c r="E5" t="n">
-        <v>61405875.49000025</v>
+        <v>119882937.3999999</v>
       </c>
       <c r="F5" t="n">
-        <v>5.117156290833353</v>
+        <v>9.990244783333321</v>
       </c>
     </row>
     <row r="6">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D6" t="n">
-        <v>2135795552.07</v>
+        <v>1899204219.51</v>
       </c>
       <c r="E6" t="n">
-        <v>-56451590.77999997</v>
+        <v>-109259092.9100001</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.704299231666664</v>
+        <v>-9.104924409166674</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D7" t="n">
-        <v>2219037258.94</v>
+        <v>2028925382.35</v>
       </c>
       <c r="E7" t="n">
-        <v>26790116.09000015</v>
+        <v>20462069.92999983</v>
       </c>
       <c r="F7" t="n">
-        <v>2.232509674166679</v>
+        <v>1.705172494166652</v>
       </c>
     </row>
     <row r="8">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D8" t="n">
-        <v>2167308510.39</v>
+        <v>1988438779.55</v>
       </c>
       <c r="E8" t="n">
-        <v>-24938632.46000004</v>
+        <v>-20024532.87000012</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.07821937166667</v>
+        <v>-1.66871107250001</v>
       </c>
     </row>
     <row r="9">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2192247142.85</v>
+        <v>2008463312.42</v>
       </c>
       <c r="D9" t="n">
-        <v>2188335533.43</v>
+        <v>1969035458.72</v>
       </c>
       <c r="E9" t="n">
-        <v>-3911609.420000076</v>
+        <v>-39427853.70000005</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.325967451666673</v>
+        <v>-3.285654475000004</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/irrbb_report.xlsx
+++ b/irrbb_calc/output/irrbb_report.xlsx
@@ -494,10 +494,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E2" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -533,28 +533,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E3" t="n">
-        <v>508247205.35</v>
+        <v>504658759.42</v>
       </c>
       <c r="F3" t="n">
-        <v>-22015439.62</v>
+        <v>-23887034.91999996</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.834619968333334</v>
+        <v>-1.99058624333333</v>
       </c>
       <c r="H3" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2038240148.16</v>
+        <v>2129901580.06</v>
       </c>
       <c r="J3" t="n">
-        <v>29776835.74000001</v>
+        <v>34903233.15999985</v>
       </c>
       <c r="K3" t="n">
-        <v>2.481402978333334</v>
+        <v>2.908602763333321</v>
       </c>
     </row>
     <row r="4">
@@ -572,28 +572,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E4" t="n">
-        <v>510874107.55</v>
+        <v>510628634.11</v>
       </c>
       <c r="F4" t="n">
-        <v>-19388537.42000002</v>
+        <v>-17917160.22999996</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.615711451666668</v>
+        <v>-1.49309668583333</v>
       </c>
       <c r="H4" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2055152460</v>
+        <v>2147240980.85</v>
       </c>
       <c r="J4" t="n">
-        <v>46689147.57999992</v>
+        <v>52242633.94999981</v>
       </c>
       <c r="K4" t="n">
-        <v>3.890762298333327</v>
+        <v>4.353552829166651</v>
       </c>
     </row>
     <row r="5">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E5" t="n">
-        <v>484366736.45</v>
+        <v>486337695.77</v>
       </c>
       <c r="F5" t="n">
-        <v>-45895908.52000004</v>
+        <v>-42208098.56999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.824659043333337</v>
+        <v>-3.5173415475</v>
       </c>
       <c r="H5" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2128346249.82</v>
+        <v>2229316540.08</v>
       </c>
       <c r="J5" t="n">
-        <v>119882937.3999999</v>
+        <v>134318193.1799998</v>
       </c>
       <c r="K5" t="n">
-        <v>9.990244783333321</v>
+        <v>11.19318276499999</v>
       </c>
     </row>
     <row r="6">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E6" t="n">
-        <v>572674499.95</v>
+        <v>567239502.7</v>
       </c>
       <c r="F6" t="n">
-        <v>42411854.98000002</v>
+        <v>38693708.36000007</v>
       </c>
       <c r="G6" t="n">
-        <v>3.534321248333335</v>
+        <v>3.224475696666672</v>
       </c>
       <c r="H6" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1899204219.51</v>
+        <v>1973036350.02</v>
       </c>
       <c r="J6" t="n">
-        <v>-109259092.9100001</v>
+        <v>-121961996.8800001</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.104924409166674</v>
+        <v>-10.16349974000001</v>
       </c>
     </row>
     <row r="7">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E7" t="n">
-        <v>528746533.87</v>
+        <v>530093342.62</v>
       </c>
       <c r="F7" t="n">
-        <v>-1516111.100000024</v>
+        <v>1547548.280000031</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1263425916666686</v>
+        <v>0.1289623566666692</v>
       </c>
       <c r="H7" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2028925382.35</v>
+        <v>2116476598.37</v>
       </c>
       <c r="J7" t="n">
-        <v>20462069.92999983</v>
+        <v>21478251.46999979</v>
       </c>
       <c r="K7" t="n">
-        <v>1.705172494166652</v>
+        <v>1.789854289166649</v>
       </c>
     </row>
     <row r="8">
@@ -728,28 +728,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E8" t="n">
-        <v>528129393.9</v>
+        <v>523259508.19</v>
       </c>
       <c r="F8" t="n">
-        <v>-2133251.070000052</v>
+        <v>-5286286.149999976</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1777709225000044</v>
+        <v>-0.4405238458333314</v>
       </c>
       <c r="H8" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1988438779.55</v>
+        <v>2073987061.46</v>
       </c>
       <c r="J8" t="n">
-        <v>-20024532.87000012</v>
+        <v>-21011285.44000006</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.66871107250001</v>
+        <v>-1.750940453333338</v>
       </c>
     </row>
     <row r="9">
@@ -767,28 +767,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E9" t="n">
-        <v>552727420.49</v>
+        <v>552265384.9</v>
       </c>
       <c r="F9" t="n">
-        <v>22464775.51999998</v>
+        <v>23719590.56</v>
       </c>
       <c r="G9" t="n">
-        <v>1.872064626666665</v>
+        <v>1.976632546666667</v>
       </c>
       <c r="H9" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1969035458.72</v>
+        <v>2049526125.86</v>
       </c>
       <c r="J9" t="n">
-        <v>-39427853.70000005</v>
+        <v>-45472221.0400002</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.285654475000004</v>
+        <v>-3.78935175333335</v>
       </c>
     </row>
   </sheetData>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D2" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D3" t="n">
-        <v>508247205.35</v>
+        <v>504658759.42</v>
       </c>
       <c r="E3" t="n">
-        <v>-22015439.62</v>
+        <v>-23887034.91999996</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.834619968333334</v>
+        <v>-1.99058624333333</v>
       </c>
     </row>
     <row r="4">
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D4" t="n">
-        <v>510874107.55</v>
+        <v>510628634.11</v>
       </c>
       <c r="E4" t="n">
-        <v>-19388537.42000002</v>
+        <v>-17917160.22999996</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.615711451666668</v>
+        <v>-1.49309668583333</v>
       </c>
     </row>
     <row r="5">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D5" t="n">
-        <v>484366736.45</v>
+        <v>486337695.77</v>
       </c>
       <c r="E5" t="n">
-        <v>-45895908.52000004</v>
+        <v>-42208098.56999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.824659043333337</v>
+        <v>-3.5173415475</v>
       </c>
     </row>
     <row r="6">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D6" t="n">
-        <v>572674499.95</v>
+        <v>567239502.7</v>
       </c>
       <c r="E6" t="n">
-        <v>42411854.98000002</v>
+        <v>38693708.36000007</v>
       </c>
       <c r="F6" t="n">
-        <v>3.534321248333335</v>
+        <v>3.224475696666672</v>
       </c>
     </row>
     <row r="7">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D7" t="n">
-        <v>528746533.87</v>
+        <v>530093342.62</v>
       </c>
       <c r="E7" t="n">
-        <v>-1516111.100000024</v>
+        <v>1547548.280000031</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1263425916666686</v>
+        <v>0.1289623566666692</v>
       </c>
     </row>
     <row r="8">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D8" t="n">
-        <v>528129393.9</v>
+        <v>523259508.19</v>
       </c>
       <c r="E8" t="n">
-        <v>-2133251.070000052</v>
+        <v>-5286286.149999976</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1777709225000044</v>
+        <v>-0.4405238458333314</v>
       </c>
     </row>
     <row r="9">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>530262644.97</v>
+        <v>528545794.34</v>
       </c>
       <c r="D9" t="n">
-        <v>552727420.49</v>
+        <v>552265384.9</v>
       </c>
       <c r="E9" t="n">
-        <v>22464775.51999998</v>
+        <v>23719590.56</v>
       </c>
       <c r="F9" t="n">
-        <v>1.872064626666665</v>
+        <v>1.976632546666667</v>
       </c>
     </row>
   </sheetData>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D2" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2038240148.16</v>
+        <v>2129901580.06</v>
       </c>
       <c r="E3" t="n">
-        <v>29776835.74000001</v>
+        <v>34903233.15999985</v>
       </c>
       <c r="F3" t="n">
-        <v>2.481402978333334</v>
+        <v>2.908602763333321</v>
       </c>
     </row>
     <row r="4">
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2055152460</v>
+        <v>2147240980.85</v>
       </c>
       <c r="E4" t="n">
-        <v>46689147.57999992</v>
+        <v>52242633.94999981</v>
       </c>
       <c r="F4" t="n">
-        <v>3.890762298333327</v>
+        <v>4.353552829166651</v>
       </c>
     </row>
     <row r="5">
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2128346249.82</v>
+        <v>2229316540.08</v>
       </c>
       <c r="E5" t="n">
-        <v>119882937.3999999</v>
+        <v>134318193.1799998</v>
       </c>
       <c r="F5" t="n">
-        <v>9.990244783333321</v>
+        <v>11.19318276499999</v>
       </c>
     </row>
     <row r="6">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1899204219.51</v>
+        <v>1973036350.02</v>
       </c>
       <c r="E6" t="n">
-        <v>-109259092.9100001</v>
+        <v>-121961996.8800001</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.104924409166674</v>
+        <v>-10.16349974000001</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2028925382.35</v>
+        <v>2116476598.37</v>
       </c>
       <c r="E7" t="n">
-        <v>20462069.92999983</v>
+        <v>21478251.46999979</v>
       </c>
       <c r="F7" t="n">
-        <v>1.705172494166652</v>
+        <v>1.789854289166649</v>
       </c>
     </row>
     <row r="8">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1988438779.55</v>
+        <v>2073987061.46</v>
       </c>
       <c r="E8" t="n">
-        <v>-20024532.87000012</v>
+        <v>-21011285.44000006</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.66871107250001</v>
+        <v>-1.750940453333338</v>
       </c>
     </row>
     <row r="9">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2008463312.42</v>
+        <v>2094998346.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1969035458.72</v>
+        <v>2049526125.86</v>
       </c>
       <c r="E9" t="n">
-        <v>-39427853.70000005</v>
+        <v>-45472221.0400002</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.285654475000004</v>
+        <v>-3.78935175333335</v>
       </c>
     </row>
   </sheetData>
